--- a/out/LSTM-mamba2_repeat_5_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7138070993914607</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7138070993914607</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.313807099391461</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.633306561630228</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.233306561630227</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-6.038105188275221e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.6961042754547568</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
-        <v>-4.284084266587161e-05</v>
+        <v>1.393284754049746</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.05524283686863281</v>
+        <v>0.1043839412694196</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.05528567771129869</v>
+        <v>0.9050139873536248</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.1305139476654237</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.05532505895131454</v>
+        <v>1.061674472939382</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.0657441158917903</v>
+        <v>0.1870911250288232</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.07632130984508013</v>
+        <v>1.305416430128927</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09045013836965464</v>
+        <v>0.2001504448110093</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1914847930539616</v>
+        <v>1.518640143900103</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1057400146230445</v>
+        <v>0.2121183915624241</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3125242269874678</v>
+        <v>1.742743104207468</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.04728850490091718</v>
+        <v>0.09572575083263495</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3012658741648996</v>
+        <v>1.721898468050247</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02276354892288144</v>
+        <v>0.04623051919669491</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2994627069131076</v>
+        <v>1.71855998084306</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01079284565446025</v>
+        <v>0.02202746602705347</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2982664066499877</v>
+        <v>1.716347619634103</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.002969585127219038</v>
+        <v>0.006523580880987169</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2934025927574381</v>
+        <v>1.707346355452162</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002051220810922444</v>
+        <v>0.004313887701662389</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2945348249114934</v>
+        <v>1.709447096823808</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001050654020751796</v>
+        <v>0.002204963193759101</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.294583547966549</v>
+        <v>1.709541551479308</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005370453133369488</v>
+        <v>0.001125481580367856</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.294605403702595</v>
+        <v>1.709586259537464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001898936636087012</v>
+        <v>0.0004203693234568383</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2944483264614935</v>
+        <v>1.70929965271882</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001031228396414692</v>
+        <v>0.0002268266796096673</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2944639070853656</v>
+        <v>1.709332699793215</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>4.676044179151377e-05</v>
+        <v>0.000106262193078166</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2944542258354111</v>
+        <v>1.709319046125635</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.807077723707194e-05</v>
+        <v>6.387685822045283e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2944635787046712</v>
+        <v>1.70934067507415</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.239825537949379e-05</v>
+        <v>3.10279205119908e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2944602827141318</v>
+        <v>1.709338859507548</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.968794623668274e-06</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2944546958334087</v>
+        <v>1.709332746370905</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>8.273743591478215e-07</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2944524919676099</v>
+        <v>1.709332779412467</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.896120456592927e-06</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2944469207777134</v>
+        <v>1.70932675070418</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.084302348447695e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2944415103077958</v>
+        <v>1.709321066170152</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2944366756734774</v>
+        <v>1.709316314894938</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2944365316895698</v>
+        <v>1.709311025747376</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2944365089552684</v>
+        <v>1.709311003013075</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2944368272354852</v>
+        <v>1.709311321293292</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.294437918481942</v>
+        <v>1.709312412539749</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2944372288748061</v>
+        <v>1.709311722932613</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2944372591872078</v>
+        <v>1.709311753245014</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2944370697346977</v>
+        <v>1.709311563792504</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2944371227814006</v>
+        <v>1.709311616839207</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2944371758281034</v>
+        <v>1.70931166988591</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2944371379376014</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2944370091098947</v>
+        <v>1.709311503167702</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2944368651259872</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2944367059858788</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2944367590325817</v>
+        <v>1.709311253090388</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2944367059858788</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2944367059858788</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2944365241114693</v>
+        <v>1.709311018169276</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.294436690829678</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2944368878602884</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.29443672872018</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.294436766610682</v>
+        <v>1.709311260668489</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2944369636412922</v>
+        <v>1.709311457699099</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.294436940906991</v>
+        <v>1.709311434964798</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2944367893449832</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2944367135639792</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2944368120792843</v>
+        <v>1.709311306137091</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2944368196573847</v>
+        <v>1.709311313715192</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2944370848908985</v>
+        <v>1.709311578948705</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2944367893449832</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2944370318441959</v>
+        <v>1.709311525902003</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2944371152033002</v>
+        <v>1.709311609261107</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2944369484850916</v>
+        <v>1.709311442542898</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2944371379376014</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2944367893449832</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2944365847362724</v>
+        <v>1.709311078794079</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2944366984077785</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2944367135639792</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2944364786428669</v>
+        <v>1.709310972700674</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2944365392676701</v>
+        <v>1.709311033325477</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2944364104399634</v>
+        <v>1.70931090449777</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2944365468457704</v>
+        <v>1.709311040903577</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2944367211420797</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2944368651259872</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2944366984077785</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.294436690829678</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2944364028618629</v>
+        <v>1.70931089691967</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2944364180180638</v>
+        <v>1.709310912075871</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2944366453610757</v>
+        <v>1.709311139418882</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2944366302048748</v>
+        <v>1.709311124262682</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2944367362982803</v>
+        <v>1.709311230356087</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2944364634866661</v>
+        <v>1.709310957544473</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2944365620019713</v>
+        <v>1.709311056059778</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2944367135639792</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.29443672872018</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2944367059858788</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2944367893449832</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2944368878602884</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2944367211420797</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2944367059858788</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2944366756734774</v>
+        <v>1.709311169731284</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2944366605172765</v>
+        <v>1.709311154575083</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2944366984077785</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2944367135639792</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2944367059858788</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_5_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.313807099391461</v>
+        <v>0.1815560313491872</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.492069948312913</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.492069948312913</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.492069948312913</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.492069948312913</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.633306561630228</v>
+        <v>-1.165695927975013</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-1.110622274398338e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.1280383453981329</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.165695927975013</v>
       </c>
       <c r="JC40" t="n">
-        <v>-4.284084266587161e-05</v>
+        <v>0.2562746149713315</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.05524283686863281</v>
+        <v>0.01919989835242345</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.233306561630227</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.05528567771129869</v>
+        <v>0.1664642666315048</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.0240061769240954</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.692069948312913</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.05532505895131454</v>
+        <v>0.1952797258315235</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.0657441158917903</v>
+        <v>0.0344125780988367</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.313807099391461</v>
+        <v>0.1815560313491873</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.07632130984508013</v>
+        <v>0.2401125784573522</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09045013836965464</v>
+        <v>0.03681499018956757</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1914847930539616</v>
+        <v>0.279332221152032</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1057400146230445</v>
+        <v>0.03901646919599322</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.313807099391461</v>
+        <v>0.1815560313491874</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3125242269874678</v>
+        <v>0.3205529551443781</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.04728850490091718</v>
+        <v>0.01760674102695103</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.492069948312913</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3012658741648996</v>
+        <v>0.3167188782069138</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02276354892288144</v>
+        <v>0.008501475406518166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.633306561630228</v>
+        <v>-1.365695927975013</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2994627069131076</v>
+        <v>0.3161023680613136</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01079284565446025</v>
+        <v>0.004047469809078052</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.6920699483129129</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2982664066499877</v>
+        <v>0.3156916565638944</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.002969585127219038</v>
+        <v>0.001196084495967923</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.01844396865081266</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2934025927574381</v>
+        <v>0.3140316762703885</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002051220810922444</v>
+        <v>0.0007889909284605235</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2945348249114934</v>
+        <v>0.3144140339097246</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001050654020751796</v>
+        <v>0.0004013734635006717</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.294583547966549</v>
+        <v>0.3144273404300697</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005370453133369488</v>
+        <v>0.0002033790624542709</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.294605403702595</v>
+        <v>0.3144314988112254</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001898936636087012</v>
+        <v>7.295914646984758e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2944483264614935</v>
+        <v>0.3143746375198194</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001031228396414692</v>
+        <v>3.790031081744733e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2944639070853656</v>
+        <v>0.3143766782595651</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>4.676044179151377e-05</v>
+        <v>1.566297871451654e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2944542258354111</v>
+        <v>0.3143700767793173</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.807077723707194e-05</v>
+        <v>7.791416526655524e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2944635787046712</v>
+        <v>0.3143699869714326</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.239825537949379e-05</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2944602827141318</v>
+        <v>0.3143655705482857</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.968794623668274e-06</v>
+        <v>-2.002720607644467e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2944546958334087</v>
+        <v>0.3143603547131102</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>8.273743591478215e-07</v>
+        <v>-2.441707244474577e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.01844396865081266</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2944524919676099</v>
+        <v>0.3143564731667906</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.896120456592927e-06</v>
+        <v>-3.834388722363316e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.01844396865081269</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2944469207777134</v>
+        <v>0.3143512444075954</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.084302348447695e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.01844396865081269</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2944415103077958</v>
+        <v>0.3143511080017884</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2944366756734774</v>
+        <v>0.3143511913608927</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.313807099391461</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2944365316895698</v>
+        <v>0.3143510473769852</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2944365089552684</v>
+        <v>0.3143510246426838</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2944368272354852</v>
+        <v>0.3143513429229006</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.313807099391461</v>
+        <v>0.1815560313491874</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.294437918481942</v>
+        <v>0.3143524341693574</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.6920699483129129</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2944372288748061</v>
+        <v>0.3143517445622215</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.233306561630227</v>
+        <v>-0.6920699483129129</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2944372591872078</v>
+        <v>0.3143517748746232</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.01844396865081259</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2944370697346977</v>
+        <v>0.3143515854221131</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2944371227814006</v>
+        <v>0.3143516384688159</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2944371758281034</v>
+        <v>0.3143516915155188</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2944371379376014</v>
+        <v>0.3143516536250168</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2944370091098947</v>
+        <v>0.3143515247973101</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2944368651259872</v>
+        <v>0.3143513808134026</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2944367059858788</v>
+        <v>0.3143512216732942</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2944367590325817</v>
+        <v>0.3143512747199971</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2944367059858788</v>
+        <v>0.3143512216732942</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2944367059858788</v>
+        <v>0.3143512216732942</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2944365241114693</v>
+        <v>0.3143510397988847</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.294436690829678</v>
+        <v>0.3143512065170934</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2944368878602884</v>
+        <v>0.3143514035477037</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.29443672872018</v>
+        <v>0.3143512444075954</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.294436766610682</v>
+        <v>0.3143512822980974</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2944369636412922</v>
+        <v>0.3143514793287076</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.294436940906991</v>
+        <v>0.3143514565944064</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2944367893449832</v>
+        <v>0.3143513050323986</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2944367135639792</v>
+        <v>0.3143512292513945</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2944368120792843</v>
+        <v>0.3143513277666997</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2944368196573847</v>
+        <v>0.3143513353448</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2944370848908985</v>
+        <v>0.3143516005783139</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2944367893449832</v>
+        <v>0.3143513050323986</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2944370318441959</v>
+        <v>0.3143515475316113</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2944371152033002</v>
+        <v>0.3143516308907157</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2944369484850916</v>
+        <v>0.3143514641725069</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2944371379376014</v>
+        <v>0.3143516536250168</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2944367893449832</v>
+        <v>0.3143513050323986</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2944365847362724</v>
+        <v>0.3143511004236879</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2944366984077785</v>
+        <v>0.3143512140951939</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2944367135639792</v>
+        <v>0.3143512292513945</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2944364786428669</v>
+        <v>0.3143509943302823</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2944365392676701</v>
+        <v>0.3143510549550855</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2944364104399634</v>
+        <v>0.3143509261273788</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2944365468457704</v>
+        <v>0.3143510625331858</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2944367211420797</v>
+        <v>0.3143512368294951</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2944368651259872</v>
+        <v>0.3143513808134026</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2944366984077785</v>
+        <v>0.3143512140951939</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.294436690829678</v>
+        <v>0.3143512065170934</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2944364028618629</v>
+        <v>0.3143509185492783</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2944364180180638</v>
+        <v>0.3143509337054791</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2944366453610757</v>
+        <v>0.314351161048491</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2944366302048748</v>
+        <v>0.3143511458922902</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2944367362982803</v>
+        <v>0.3143512519856957</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2944364634866661</v>
+        <v>0.3143509791740814</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2944365620019713</v>
+        <v>0.3143510776893867</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2944367135639792</v>
+        <v>0.3143512292513945</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.29443672872018</v>
+        <v>0.3143512444075954</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2944367059858788</v>
+        <v>0.3143512216732942</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2944367893449832</v>
+        <v>0.3143513050323986</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2944368878602884</v>
+        <v>0.3143514035477037</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2944367211420797</v>
+        <v>0.3143512368294951</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2944367059858788</v>
+        <v>0.3143512216732942</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2944366756734774</v>
+        <v>0.3143511913608927</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2944366605172765</v>
+        <v>0.3143511762046919</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2944366984077785</v>
+        <v>0.3143512140951939</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2944367135639792</v>
+        <v>0.3143512292513945</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2944367059858788</v>
+        <v>0.3143512216732942</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_5_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.197488397359848</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.09720161557197571</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.3700000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01391308382153511</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.1815560313491872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.02094205468893051</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.492069948312913</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.03445659577846527</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.03911580890417099</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.03837877511978149</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.03636256605386734</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.03195812553167343</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.03056984394788742</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.03124690055847168</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.03181076794862747</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.02982679754495621</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.03122454881668091</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.03282299637794495</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0348585918545723</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.03425455838441849</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.03527554124593735</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.03475217521190643</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.03147657960653305</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.02684861421585083</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01930493861436844</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.02315482869744301</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.02719664573669434</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.02918706089258194</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0305156484246254</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.03172625601291656</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.02635245770215988</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.02546628564596176</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.02711597084999084</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.02841699123382568</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.03091778606176376</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.365695927975013</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.02932213991880417</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.365695927975013</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.02731910347938538</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.365695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.01886745169758797</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.492069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.006245695054531097</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.492069948312913</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.004019543528556824</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.492069948312913</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.009232096374034882</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.165695927975013</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-1.110622274398338e-05</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.1280383453981329</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.01237287372350693</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.165695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>0.2562746149713315</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.01919989835242345</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.008279230445623398</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.365695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.1664642666315048</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.0240061769240954</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.005171287804841995</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.692069948312913</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.1952797258315235</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.0344125780988367</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.00682385265827179</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.1815560313491873</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.2401125784573522</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03681499018956757</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01260565407574177</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.279332221152032</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.03901646919599322</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.001882385462522507</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1815560313491874</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3205529551443781</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.01760674102695103</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.003403030335903168</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.492069948312913</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3167188782069138</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.008501475406518166</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01510432735085487</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.365695927975013</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3161023680613136</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.004047469809078052</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.003445174545049667</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6920699483129129</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3156916565638944</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.001196084495967923</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01340528391301632</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.01844396865081266</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.3140316762703885</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0007889909284605235</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.02621141262352467</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3144140339097246</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0004013734635006717</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.02708001062273979</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3144273404300697</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0002033790624542709</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.02649218216538429</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3144314988112254</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>7.295914646984758e-05</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02625242248177528</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3143746375198194</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>3.790031081744733e-05</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.02214033715426922</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.3143766782595651</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>1.566297871451654e-05</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.02066918089985847</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3143700767793173</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.791416526655524e-06</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01808582805097103</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3143699869714326</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.176214944912711e-06</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.009693777188658714</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3143655705482857</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.002720607644467e-06</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.03627874329686165</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3143603547131102</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.441707244474577e-06</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.008862178772687912</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.01844396865081266</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3143564731667906</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.834388722363316e-06</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.005929261445999146</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.01844396865081269</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3143512444075954</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.00555061548948288</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.01844396865081269</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3143511080017884</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01401180773973465</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3143511913608927</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01878692582249641</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3143510473769852</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.02661953121423721</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3143510246426838</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.03295540064573288</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3143513429229006</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.02367006056010723</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.1815560313491874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3143524341693574</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01144170761108398</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6920699483129129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3143517445622215</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0203343890607357</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6920699483129129</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3143517748746232</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.001454222947359085</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.01844396865081259</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3143515854221131</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.02626388520002365</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3143516384688159</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.04257467016577721</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3143516915155188</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.05075420066714287</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3143516536250168</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.05083488672971725</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3143515247973101</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.04468318819999695</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3143513808134026</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.03730104863643646</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3143512216732942</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.02907603979110718</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3143512747199971</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.02073870040476322</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3143512216732942</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01648791134357452</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3143512216732942</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.02168203331530094</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3143510397988847</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.02171804383397102</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3143512065170934</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.009363805875182152</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3143514035477037</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.007974909618496895</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3143512444075954</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01682764291763306</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3143512822980974</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01800339482724667</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3143514793287076</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01061969995498657</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3143514565944064</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01128108613193035</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3143513050323986</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01783135533332825</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3143512292513945</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.02115587331354618</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3143513277666997</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.02635383605957031</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3143513353448</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01764548197388649</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3143516005783139</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01761232689023018</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3143513050323986</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.02027123980224133</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3143515475316113</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01408836618065834</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3143516308907157</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.02586214616894722</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3143514641725069</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01282951049506664</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3143516536250168</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01236002333462238</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3143513050323986</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.02028701640665531</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3143511004236879</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.02517868205904961</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3143512140951939</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.02483319491147995</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3143512292513945</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0241067036986351</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3143509943302823</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01628303527832031</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3143510549550855</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01447296515107155</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3143509261273788</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.02415570244193077</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3143510625331858</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01532118767499924</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3143512368294951</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.005998231470584869</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3143513808134026</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01018473692238331</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3143512140951939</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.008507819846272469</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3143512065170934</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.008486252278089523</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3143509185492783</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.01203750446438789</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3143509337054791</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.009019976481795311</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.314351161048491</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.01219422928988934</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3143511458922902</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.004020825028419495</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3143512519856957</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.004295371472835541</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3143509791740814</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.00824592262506485</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3143510776893867</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.00836428627371788</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3143512292513945</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.008186481893062592</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3143512444075954</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01022953167557716</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3143512216732942</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.012484360486269</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3143513050323986</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.008095972239971161</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3143514035477037</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.007597466930747032</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3143512368294951</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.01065546460449696</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3143512216732942</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.01210570335388184</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3143511913608927</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01315875351428986</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3143511762046919</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.01072495430707932</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3143512140951939</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01104773581027985</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3143512292513945</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01257154904305935</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3143512216732942</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>
